--- a/LISTAS_ORDENADAS/MA/Soportes y escuadras/SOP MENSULA REFORZADA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Soportes y escuadras/SOP MENSULA REFORZADA DISMAY.xlsx
@@ -890,13 +890,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45202.60866480736</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -928,21 +924,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="13.5" customHeight="1" s="1" thickBot="1"/>
     <row r="27" ht="19.5" customHeight="1" s="1" thickBot="1" thickTop="1">
       <c r="A27" s="23" t="inlineStr">
@@ -955,7 +936,6 @@
       <c r="D27" s="25" t="n"/>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="1" thickTop="1"/>
-    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -987,7 +967,7 @@
       </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="29" t="n">
-        <v>1515.93</v>
+        <v>1515.938</v>
       </c>
       <c r="E31" s="30" t="n"/>
       <c r="F31" s="30" t="n"/>
@@ -1005,7 +985,7 @@
       </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="29" t="n">
-        <v>1998.93</v>
+        <v>1998.938</v>
       </c>
       <c r="E32" s="30" t="n"/>
       <c r="F32" s="30" t="n"/>
@@ -1023,7 +1003,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="31" t="n">
-        <v>2529.18</v>
+        <v>2529.188</v>
       </c>
       <c r="E33" s="30" t="n"/>
       <c r="F33" s="30" t="n"/>
@@ -1041,7 +1021,7 @@
       </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="31" t="n">
-        <v>2852.06</v>
+        <v>2852.063</v>
       </c>
       <c r="E34" s="30" t="n"/>
       <c r="F34" s="30" t="n"/>
@@ -1049,14 +1029,9 @@
     <row r="35">
       <c r="E35" s="30" t="n"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="4" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
@@ -1066,15 +1041,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A27:D27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
